--- a/output/pdf_financials_xlsx/FLNT.xlsx
+++ b/output/pdf_financials_xlsx/FLNT.xlsx
@@ -927,10 +927,10 @@
         <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.492</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>1.297</v>
       </c>
     </row>
     <row r="13">
@@ -1712,10 +1712,10 @@
         <v>-12.92</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>1.272</v>
+        <v>0.78</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>2.071</v>
+        <v>0.774</v>
       </c>
     </row>
     <row r="28">
@@ -1802,10 +1802,10 @@
         <v>-12.519</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>1.538</v>
+        <v>1.046</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>2.327</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="30">
@@ -1847,10 +1847,10 @@
         <v>-1.909126260970347</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>0.2164508256937545</v>
+        <v>0.1472090791129175</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>0.4126998765624779</v>
+        <v>0.1826733445893219</v>
       </c>
     </row>
     <row r="31">
@@ -1963,28 +1963,28 @@
         <v>24.409</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>11.503</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>4.649</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>10.838</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>7.109</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>30.477</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>21.68</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>3.134</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>9.696</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>10.957</v>
@@ -2049,28 +2049,28 @@
         <v>24.409</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>11.503</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>4.649</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>10.838</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>7.109</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>30.477</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>21.68</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>3.134</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>9.696</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>10.957</v>
@@ -2565,28 +2565,28 @@
         <v>0.114</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>16.151</v>
+        <v>4.648</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>12.401</v>
+        <v>7.752</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>13.864</v>
+        <v>3.026</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>9.801</v>
+        <v>2.692</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>32.29</v>
+        <v>1.813</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>23.741</v>
+        <v>2.061</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>5.575</v>
+        <v>2.441</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>12.644</v>
+        <v>2.948</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>3.536</v>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>5.778</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0</v>
+        <v>-1.577</v>
       </c>
       <c r="G124" s="3" t="n">
         <v>0</v>
@@ -5895,10 +5895,10 @@
         <v>0</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>5.778</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>-1.577</v>
       </c>
       <c r="G125" s="3" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -9950,7 +9950,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -10478,7 +10478,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -15874,7 +15874,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -16248,7 +16248,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -17472,7 +17472,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -31782,7 +31782,11 @@
           <t>Onerous lease payments</t>
         </is>
       </c>
-      <c r="D343" t="inlineStr"/>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E343" t="inlineStr">
         <is>
           <t>-</t>
@@ -34880,7 +34884,11 @@
           <t>Onerous lease payments 9</t>
         </is>
       </c>
-      <c r="D384" t="inlineStr"/>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E384" t="inlineStr">
         <is>
           <t>-</t>
@@ -46212,7 +46220,7 @@
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
@@ -46286,7 +46294,7 @@
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E537" t="inlineStr">
@@ -47830,7 +47838,7 @@
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E558" t="inlineStr">
@@ -52582,7 +52590,7 @@
       </c>
       <c r="D622" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E622" t="inlineStr">
@@ -53364,7 +53372,7 @@
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E633" t="inlineStr">
@@ -54686,7 +54694,7 @@
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E651" t="inlineStr">
@@ -56938,7 +56946,7 @@
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E681" t="inlineStr">
@@ -58922,7 +58930,7 @@
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E708" t="inlineStr">
@@ -60912,7 +60920,7 @@
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E735" t="inlineStr">
@@ -62482,7 +62490,7 @@
       </c>
       <c r="D756" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E756" s="5" t="n">

--- a/output/pdf_financials_xlsx/FLNT.xlsx
+++ b/output/pdf_financials_xlsx/FLNT.xlsx
@@ -1725,19 +1725,19 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>15.543</v>
+        <v>5.715</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>14.332</v>
+        <v>5.651</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>10.001</v>
+        <v>3.376</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>8.709</v>
+        <v>3.445</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>6.319</v>
+        <v>1.371</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>1.023</v>
@@ -1770,19 +1770,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>19.06</v>
+        <v>9.231999999999999</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-54.92</v>
+        <v>-63.601</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-48.522</v>
+        <v>-55.147</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-30.641</v>
+        <v>-35.905</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-26.743</v>
+        <v>-31.691</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-1.749</v>
@@ -1815,19 +1815,19 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>3.417068850531026</v>
+        <v>1.655109109554167</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-13.19805249422044</v>
+        <v>-15.28421953177193</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-17.92722261426655</v>
+        <v>-20.37493395797695</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-8.57938047918644</v>
+        <v>-10.05328338191277</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-7.06865927280801</v>
+        <v>-8.376505291648604</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>-0.3767350490681785</v>
@@ -4811,40 +4811,40 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>5.715</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>5.651</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>3.376</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>3.445</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>1.371</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>1.023</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>1.824</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.669</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.401</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.256</v>
       </c>
     </row>
     <row r="101">
@@ -5336,31 +5336,31 @@
         <v>0</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>3.063</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.575</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>1.915</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>1.312</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>1.678</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>0.788</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>1.415</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>4.951</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="113">
@@ -24128,7 +24128,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -25030,7 +25030,11 @@
           <t>Proceeds on disposal of property, plant and equipment 5</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr"/>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E252" t="inlineStr">
         <is>
           <t>-</t>
@@ -26142,7 +26146,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -27012,7 +27016,11 @@
           <t>Net proceeds on disposal of property, plant and equipment 3</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr"/>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E279" t="inlineStr">
         <is>
           <t>-</t>
@@ -31406,7 +31414,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -32698,7 +32706,11 @@
           <t>Net proceeds on disposal of property, plant and equipment 4</t>
         </is>
       </c>
-      <c r="D355" t="inlineStr"/>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E355" t="inlineStr">
         <is>
           <t>-</t>
@@ -34580,7 +34592,7 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
@@ -35492,7 +35504,11 @@
           <t>Net proceeds on disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D392" t="inlineStr"/>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E392" t="inlineStr">
         <is>
           <t>-</t>
@@ -39684,7 +39700,7 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
@@ -43434,7 +43450,7 @@
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E498" s="5" t="n">
@@ -46012,7 +46028,7 @@
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E533" t="inlineStr">
@@ -46066,10 +46082,10 @@
         </is>
       </c>
       <c r="O533" s="5" t="n">
-        <v>-0.266</v>
+        <v>0.266</v>
       </c>
       <c r="P533" s="5" t="n">
-        <v>-0.256</v>
+        <v>0.256</v>
       </c>
     </row>
     <row r="534">
@@ -47702,7 +47718,7 @@
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E556" t="inlineStr">
@@ -47741,16 +47757,16 @@
         </is>
       </c>
       <c r="L556" s="5" t="n">
-        <v>-0.669</v>
+        <v>0.669</v>
       </c>
       <c r="M556" s="5" t="n">
-        <v>-0.5629999999999999</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="N556" s="5" t="n">
-        <v>-0.401</v>
+        <v>0.401</v>
       </c>
       <c r="O556" s="5" t="n">
-        <v>-0.266</v>
+        <v>0.266</v>
       </c>
       <c r="P556" t="inlineStr">
         <is>
@@ -54468,7 +54484,7 @@
       </c>
       <c r="D648" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E648" t="inlineStr">
@@ -54492,10 +54508,10 @@
         </is>
       </c>
       <c r="I648" s="5" t="n">
-        <v>-1.371</v>
+        <v>1.371</v>
       </c>
       <c r="J648" s="5" t="n">
-        <v>-1.023</v>
+        <v>1.023</v>
       </c>
       <c r="K648" t="inlineStr">
         <is>
@@ -56732,7 +56748,7 @@
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
@@ -56751,10 +56767,10 @@
         </is>
       </c>
       <c r="H678" s="5" t="n">
-        <v>-3.445</v>
+        <v>3.445</v>
       </c>
       <c r="I678" s="5" t="n">
-        <v>-1.371</v>
+        <v>1.371</v>
       </c>
       <c r="J678" t="inlineStr">
         <is>
@@ -58712,7 +58728,7 @@
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E705" t="inlineStr">
@@ -58726,10 +58742,10 @@
         </is>
       </c>
       <c r="G705" s="5" t="n">
-        <v>-3.376</v>
+        <v>3.376</v>
       </c>
       <c r="H705" s="5" t="n">
-        <v>-3.445</v>
+        <v>3.445</v>
       </c>
       <c r="I705" t="inlineStr">
         <is>
@@ -60690,7 +60706,7 @@
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E732" t="inlineStr">
@@ -60699,10 +60715,10 @@
         </is>
       </c>
       <c r="F732" s="5" t="n">
-        <v>-5.651</v>
+        <v>5.651</v>
       </c>
       <c r="G732" s="5" t="n">
-        <v>-3.376</v>
+        <v>3.376</v>
       </c>
       <c r="H732" t="inlineStr">
         <is>
@@ -62272,14 +62288,14 @@
       </c>
       <c r="D753" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E753" s="5" t="n">
-        <v>-5.715</v>
+        <v>5.715</v>
       </c>
       <c r="F753" s="5" t="n">
-        <v>-5.651</v>
+        <v>5.651</v>
       </c>
       <c r="G753" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/FLNT.xlsx
+++ b/output/pdf_financials_xlsx/FLNT.xlsx
@@ -1084,7 +1084,7 @@
         <v>-58.523</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>-39.35</v>
+        <v>-35.907</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>-33.062</v>
@@ -1129,7 +1129,7 @@
         <v>12.793</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>3.445</v>
+        <v>0.002</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>1.495</v>
@@ -1299,22 +1299,22 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>-17.247</v>
+        <v>-8.266</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>-124.887</v>
+        <v>-64.43600000000001</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>-45.73</v>
+        <v>-32.937</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>-35.905</v>
+        <v>-32.46</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>-31.567</v>
+        <v>-30.072</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>-4.712</v>
+        <v>-6.652</v>
       </c>
       <c r="H20" s="1" t="inlineStr">
         <is>
@@ -1322,13 +1322,13 @@
         </is>
       </c>
       <c r="I20" s="3" t="n">
-        <v>-9.308</v>
+        <v>-9.295999999999999</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>-12.979</v>
+        <v>-12.431</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>-12.907</v>
+        <v>-12.894</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>1.272</v>
@@ -1689,7 +1689,7 @@
         <v>-58.523</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-39.35</v>
+        <v>-35.907</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-33.062</v>
@@ -1779,7 +1779,7 @@
         <v>-55.147</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-35.905</v>
+        <v>-32.462</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-31.691</v>
@@ -1824,7 +1824,7 @@
         <v>-20.37493395797695</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-10.05328338191277</v>
+        <v>-9.089254564647051</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>-8.376505291648604</v>
@@ -1869,7 +1869,7 @@
         <v>-21.85978162431864</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-8.754764930114359</v>
+        <v>-0.005569944579051438</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>-4.521807513157099</v>
@@ -3059,31 +3059,31 @@
         <v>38.506</v>
       </c>
       <c r="C59" s="3" t="n">
-        <v>49.892</v>
+        <v>18.904</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>38.088</v>
+        <v>0</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>26.765</v>
+        <v>0</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>20.937</v>
+        <v>0</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>33.584</v>
+        <v>0</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>7.018</v>
+        <v>-6.824</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>13.36</v>
+        <v>-0.669</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>9.145</v>
+        <v>0</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>1.455</v>
+        <v>0</v>
       </c>
       <c r="L59" s="3" t="n">
         <v>1.189</v>
@@ -3148,28 +3148,28 @@
         <v>0</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>5.351</v>
+        <v>43.439</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>1.764</v>
+        <v>28.529</v>
       </c>
       <c r="F61" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>0</v>
+        <v>18.782</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>6.67</v>
+        <v>20.512</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>0</v>
+        <v>14.029</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0</v>
+        <v>9.145</v>
       </c>
       <c r="K61" s="3" t="n">
-        <v>0</v>
+        <v>1.455</v>
       </c>
       <c r="L61" s="3" t="n">
         <v>0</v>
@@ -3400,10 +3400,10 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>36.117</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>22.763</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>0</v>
@@ -5241,40 +5241,40 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>8.878</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>7.465</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>2.526</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.949</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>0.299</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>1.362</v>
       </c>
       <c r="H110" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>0.432</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>0</v>
+        <v>0.268</v>
       </c>
       <c r="K110" s="3" t="n">
-        <v>0</v>
+        <v>0.317</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>0.278</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>0.147</v>
       </c>
     </row>
     <row r="111">
@@ -5327,13 +5327,13 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>0.699</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.311</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>1.927</v>
       </c>
       <c r="E112" s="3" t="n">
         <v>3.063</v>
@@ -5370,7 +5370,7 @@
         </is>
       </c>
       <c r="B113" s="3" t="n">
-        <v>0</v>
+        <v>-0.308</v>
       </c>
       <c r="C113" s="3" t="n">
         <v>0</v>
@@ -5477,10 +5477,10 @@
         <v>0</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="K115" s="3" t="n">
         <v>0</v>
@@ -5508,19 +5508,19 @@
         <v>0</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0</v>
+        <v>-0.063</v>
       </c>
       <c r="F116" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0</v>
+        <v>-0.374</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>0</v>
+        <v>-0.335</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>0</v>
+        <v>-0.022</v>
       </c>
       <c r="J116" s="3" t="n">
         <v>0</v>
@@ -8642,7 +8642,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>OtherIntangibleAssets</t>
+          <t>GoodwillAndOtherIntangibleAssets</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -14420,7 +14420,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>OtherIntangibleAssets</t>
+          <t>GoodwillAndOtherIntangibleAssets</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -16788,7 +16788,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>OtherIntangibleAssets</t>
+          <t>GoodwillAndOtherIntangibleAssets</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -18174,7 +18174,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>OtherIntangibleAssets</t>
+          <t>GoodwillAndOtherIntangibleAssets</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -20446,7 +20446,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>OtherIntangibleAssets</t>
+          <t>GoodwillAndOtherIntangibleAssets</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -24352,7 +24352,11 @@
           <t>Accretion expense 12</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
@@ -26070,7 +26074,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D266" t="inlineStr"/>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E266" t="inlineStr">
         <is>
           <t>-</t>
@@ -26354,7 +26362,11 @@
           <t>Accretion expense 8</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr"/>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E270" t="inlineStr">
         <is>
           <t>-</t>
@@ -27752,7 +27764,11 @@
           <t>Accretion expense 9</t>
         </is>
       </c>
-      <c r="D289" t="inlineStr"/>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E289" t="inlineStr">
         <is>
           <t>-</t>
@@ -28284,7 +28300,11 @@
           <t>Proceeds from long-term investments</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr"/>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E296" t="inlineStr">
         <is>
           <t>-</t>
@@ -28732,7 +28752,11 @@
           <t>Accretion expense 11</t>
         </is>
       </c>
-      <c r="D302" t="inlineStr"/>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E302" t="inlineStr">
         <is>
           <t>-</t>
@@ -29326,7 +29350,11 @@
           <t>Purchase of intangible assets 4</t>
         </is>
       </c>
-      <c r="D310" t="inlineStr"/>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E310" t="inlineStr">
         <is>
           <t>-</t>
@@ -30062,7 +30090,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D320" t="inlineStr"/>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E320" t="inlineStr">
         <is>
           <t>-</t>
@@ -32246,7 +32278,11 @@
           <t>Deferred income tax recovery 3</t>
         </is>
       </c>
-      <c r="D349" t="inlineStr"/>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E349" t="inlineStr">
         <is>
           <t>-</t>
@@ -32784,7 +32820,11 @@
           <t>Purchase of intangible assets 5</t>
         </is>
       </c>
-      <c r="D356" t="inlineStr"/>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E356" t="inlineStr">
         <is>
           <t>-</t>
@@ -35582,7 +35622,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D393" t="inlineStr"/>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E393" t="inlineStr">
         <is>
           <t>-</t>
@@ -39924,7 +39968,11 @@
           <t>Non-cash accretion expense (note 15)</t>
         </is>
       </c>
-      <c r="D451" t="inlineStr"/>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E451" t="inlineStr">
         <is>
           <t>-</t>
@@ -40746,7 +40794,11 @@
           <t>Proceeds on disposition of property, plant and equipment, net (note 5)</t>
         </is>
       </c>
-      <c r="D462" t="inlineStr"/>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E462" t="inlineStr">
         <is>
           <t>-</t>
@@ -42102,7 +42154,11 @@
           <t>Deferred income tax recovery (note 17)</t>
         </is>
       </c>
-      <c r="D480" t="inlineStr"/>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E480" s="5" t="n">
         <v>-6.799</v>
       </c>
@@ -42250,7 +42306,11 @@
           <t>Non-cash accretion expense (note 16)</t>
         </is>
       </c>
-      <c r="D482" t="inlineStr"/>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E482" t="inlineStr">
         <is>
           <t>-</t>
@@ -43678,7 +43738,11 @@
           <t>Non-cash accretion expense (notes 4 and 12)</t>
         </is>
       </c>
-      <c r="D501" t="inlineStr"/>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E501" s="5" t="n">
         <v>8.878</v>
       </c>
@@ -44360,7 +44424,11 @@
           <t>Proceeds on disposition of property, plant and equipment, net</t>
         </is>
       </c>
-      <c r="D510" t="inlineStr"/>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E510" s="5" t="n">
         <v>0.699</v>
       </c>
@@ -44584,7 +44652,11 @@
           <t>Acquisition of business, net (note 3)</t>
         </is>
       </c>
-      <c r="D513" t="inlineStr"/>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>PurchaseOfBusiness</t>
+        </is>
+      </c>
       <c r="E513" s="5" t="n">
         <v>-0.308</v>
       </c>
@@ -52888,9 +52960,13 @@
           <t>Loss from continuing operations</t>
         </is>
       </c>
-      <c r="D626" t="inlineStr"/>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E626" s="5" t="n">
-        <v>8.266</v>
+        <v>-8.266</v>
       </c>
       <c r="F626" s="5" t="n">
         <v>-64.43600000000001</v>
@@ -55614,7 +55690,11 @@
           <t>Loss from continuing operations</t>
         </is>
       </c>
-      <c r="D663" t="inlineStr"/>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E663" t="inlineStr">
         <is>
           <t>-</t>
@@ -57454,7 +57534,11 @@
           <t>Deferred income tax recovery 16</t>
         </is>
       </c>
-      <c r="D688" t="inlineStr"/>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E688" t="inlineStr">
         <is>
           <t>-</t>
@@ -61688,7 +61772,11 @@
           <t>Loss from continuing operations</t>
         </is>
       </c>
-      <c r="D745" t="inlineStr"/>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E745" t="inlineStr">
         <is>
           <t>-</t>
